--- a/tests/TaggingAutomation/TaggingAutomationData.xlsx
+++ b/tests/TaggingAutomation/TaggingAutomationData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sarvam API\tests\TaggingAutomation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{994CC33A-FE94-46C5-9A49-4A8D3634D65B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9BB74A1-CDB5-4C2C-8F90-384577800B95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,11 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="228">
   <si>
     <t xml:space="preserve">Sno </t>
   </si>
@@ -689,16 +688,90 @@
     <t>123 &lt;sub&gt; this is tesr 123 &lt;/sub&gt; 234</t>
   </si>
   <si>
-    <t>&lt;n1&gt;,&lt;n2&gt;,&lt;n3&gt;</t>
-  </si>
-  <si>
     <t>delh12sadf1234</t>
   </si>
   <si>
     <t>123delh12</t>
   </si>
   <si>
-    <t>123,123,234</t>
+    <t>Office No 7,8,9, 10, ABC East, 3rd Floor, Near Prozone Mall, Plot No D-5/1-A,B,C, Chikalthana MIDC A</t>
+  </si>
+  <si>
+    <t>Special Characters – Decimal, Hyphen, Colon, and Currency Format</t>
+  </si>
+  <si>
+    <t>Special Characters – Comma, Hyphen, Forward Slash, Alphanumeric Address</t>
+  </si>
+  <si>
+    <t>Special Characters – Fraction (½), Numeric Values, and Sentence Punctuation</t>
+  </si>
+  <si>
+    <t>&lt;n1&gt;,&lt;n2&gt;,&lt;n3&gt;,&lt;n4&gt;,&lt;n5&gt;,&lt;n6&gt;,&lt;n7&gt;</t>
+  </si>
+  <si>
+    <t>7,8,9, 10,3,5,1</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The policy period for Care Corona Kavach is </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>9½ months</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+  </si>
+  <si>
+    <t>43. 44-45-46: INR 47.48 46-34-53</t>
+  </si>
+  <si>
+    <t>44-45-46,47.48,46-34-53</t>
+  </si>
+  <si>
+    <t>&lt;an1&gt;,&lt;n1&gt;,&lt;an2&gt;</t>
+  </si>
+  <si>
+    <t>&lt;n1&gt;,&lt;sub1&gt;,&lt;n2&gt;,&lt;/sub1&gt;,&lt;n3&gt;</t>
+  </si>
+  <si>
+    <t>123,&lt;sub&gt;,123,&lt;/sub&gt;234</t>
+  </si>
+  <si>
+    <t>Product name with inch size and image token</t>
+  </si>
+  <si>
+    <t>Feltron 80 cm (32 inch) HD Ready Smart LED TV (FT-3209SFL) img6.</t>
+  </si>
+  <si>
+    <t>&lt;n1&gt;,&lt;n2&gt;,&lt;n3&gt;,&lt;n4&gt;</t>
+  </si>
+  <si>
+    <t>80,32 ,3209,6</t>
+  </si>
+  <si>
+    <t>dated December 19, 2012.</t>
+  </si>
+  <si>
+    <t>Date with ,  seprator</t>
+  </si>
+  <si>
+    <t>19,2012</t>
   </si>
 </sst>
 </file>
@@ -1161,14 +1234,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R67"/>
+  <dimension ref="A1:R72"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="8.7265625" style="16" customWidth="1"/>
     <col min="2" max="2" width="18" style="5" customWidth="1"/>
     <col min="3" max="3" width="67.81640625" style="13" customWidth="1"/>
-    <col min="4" max="4" width="31.36328125" customWidth="1"/>
-    <col min="5" max="5" width="29.453125" customWidth="1"/>
+    <col min="4" max="4" width="35.453125" customWidth="1"/>
+    <col min="5" max="5" width="33" customWidth="1"/>
     <col min="6" max="6" width="47.453125" style="10" customWidth="1"/>
     <col min="7" max="7" width="32.1796875" customWidth="1"/>
   </cols>
@@ -2633,7 +2706,7 @@
         <v>53</v>
       </c>
       <c r="F65" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G65" t="s">
         <v>53</v>
@@ -2656,7 +2729,7 @@
         <v>53</v>
       </c>
       <c r="F66" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G66" t="s">
         <v>53</v>
@@ -2673,16 +2746,119 @@
         <v>206</v>
       </c>
       <c r="D67" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="E67" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="F67" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="G67" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="58">
+      <c r="A68" s="16">
+        <v>70</v>
+      </c>
+      <c r="B68" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="G67" t="s">
-        <v>207</v>
+      <c r="C68" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="D68" t="s">
+        <v>218</v>
+      </c>
+      <c r="E68" t="s">
+        <v>218</v>
+      </c>
+      <c r="F68" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="G68" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="72.5">
+      <c r="A69" s="16">
+        <v>71</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="D69" t="s">
+        <v>213</v>
+      </c>
+      <c r="E69" t="s">
+        <v>213</v>
+      </c>
+      <c r="F69" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="G69" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="72.5">
+      <c r="A70" s="16">
+        <v>72</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="43.5">
+      <c r="A71" s="16">
+        <v>73</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="D71" t="s">
+        <v>223</v>
+      </c>
+      <c r="E71" t="s">
+        <v>223</v>
+      </c>
+      <c r="F71" t="s">
+        <v>224</v>
+      </c>
+      <c r="G71" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" s="16">
+        <v>74</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="C72" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="D72" t="s">
+        <v>21</v>
+      </c>
+      <c r="E72" t="s">
+        <v>21</v>
+      </c>
+      <c r="F72" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="G72" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
